--- a/make_interface/Tohoku Robust Regression.xlsx
+++ b/make_interface/Tohoku Robust Regression.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-20.83°</t>
+          <t>-5.60°</t>
         </is>
       </c>
     </row>
@@ -456,7 +456,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-18.85°</t>
+          <t>-8.46°</t>
         </is>
       </c>
     </row>
@@ -466,7 +466,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-16.79°</t>
+          <t>-11.27°</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-14.66°</t>
+          <t>-14.00°</t>
         </is>
       </c>
     </row>
@@ -486,7 +486,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.47°</t>
+          <t>-16.64°</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-10.22°</t>
+          <t>-19.17°</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-7.93°</t>
+          <t>-21.58°</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-5.60°</t>
+          <t>-23.89°</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-3.23°</t>
+          <t>-26.08°</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.85°</t>
+          <t>-28.15°</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.53°</t>
+          <t>-30.11°</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3.91°</t>
+          <t>-31.95°</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6.27°</t>
+          <t>-33.70°</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8.59°</t>
+          <t>-35.34°</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10.87°</t>
+          <t>-36.89°</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13.10°</t>
+          <t>-38.35°</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15.28°</t>
+          <t>-39.73°</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17.38°</t>
+          <t>-41.02°</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18.94°</t>
+          <t>-42.25°</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>-43.41°</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>-44.49°</t>
         </is>
       </c>
     </row>
